--- a/new-info41/web.xlsx
+++ b/new-info41/web.xlsx
@@ -4,12 +4,16 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="16575" windowHeight="10080"/>
+    <workbookView windowWidth="25380" windowHeight="8355"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet5" sheetId="10" r:id="rId1"/>
-    <sheet name="Sheet4" sheetId="9" r:id="rId2"/>
-    <sheet name="Sheet6" sheetId="11" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="14" r:id="rId1"/>
+    <sheet name="Sheet5" sheetId="10" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="15" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="13" r:id="rId4"/>
+    <sheet name="Sheet4" sheetId="16" r:id="rId5"/>
+    <sheet name="Sheet6" sheetId="17" r:id="rId6"/>
+    <sheet name="Sheet7" sheetId="18" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,39 +33,600 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="198">
   <si>
     <t>domain</t>
   </si>
   <si>
+    <t>color</t>
+  </si>
+  <si>
+    <t>color2</t>
+  </si>
+  <si>
+    <t>farikal.site</t>
+  </si>
+  <si>
+    <t>#664b3a</t>
+  </si>
+  <si>
+    <t>voidspire.cloud</t>
+  </si>
+  <si>
+    <t>#e07563</t>
+  </si>
+  <si>
+    <t>lunathor.cloud</t>
+  </si>
+  <si>
+    <t>#41bbcb</t>
+  </si>
+  <si>
+    <t>finonewsx.com</t>
+  </si>
+  <si>
+    <t>#6090b8</t>
+  </si>
+  <si>
+    <t>witchetty.fun</t>
+  </si>
+  <si>
+    <t>#4d613c</t>
+  </si>
+  <si>
+    <t>spuddles.fun</t>
+  </si>
+  <si>
+    <t>#707899</t>
+  </si>
+  <si>
+    <t>moilfuns.fun</t>
+  </si>
+  <si>
+    <t>#70c588</t>
+  </si>
+  <si>
     <t>color1</t>
   </si>
   <si>
-    <t>color2</t>
-  </si>
-  <si>
-    <t>read.susurrop.top</t>
-  </si>
-  <si>
-    <t>#1781b5</t>
-  </si>
-  <si>
-    <t>read.panoramafind.fun</t>
-  </si>
-  <si>
-    <t>#Fd8134</t>
-  </si>
-  <si>
-    <t>invicts.site</t>
-  </si>
-  <si>
-    <t>#e7bf40</t>
-  </si>
-  <si>
-    <t>halcyons.cloud</t>
-  </si>
-  <si>
-    <t>#a4dd52</t>
+    <t>info</t>
+  </si>
+  <si>
+    <t>json</t>
+  </si>
+  <si>
+    <t>sylthyn.com</t>
+  </si>
+  <si>
+    <t>#6ae966</t>
+  </si>
+  <si>
+    <t>vegimite.fun</t>
+  </si>
+  <si>
+    <t>#718771</t>
+  </si>
+  <si>
+    <t>casumartzu.site</t>
+  </si>
+  <si>
+    <t>#ff978a</t>
+  </si>
+  <si>
+    <t>jabot.cloud</t>
+  </si>
+  <si>
+    <t>#00000e</t>
+  </si>
+  <si>
+    <t>epaulette.cloud</t>
+  </si>
+  <si>
+    <t>#a515f9</t>
+  </si>
+  <si>
+    <t>play.seatranquil.com</t>
+  </si>
+  <si>
+    <t>#6b496a</t>
+  </si>
+  <si>
+    <t>sec.seatranquil.com</t>
+  </si>
+  <si>
+    <t>#e6e3c3</t>
+  </si>
+  <si>
+    <t>#4167b1</t>
+  </si>
+  <si>
+    <t>#def0f9</t>
+  </si>
+  <si>
+    <t>#d62828</t>
+  </si>
+  <si>
+    <t>#f8e9a1</t>
+  </si>
+  <si>
+    <t>#e58889</t>
+  </si>
+  <si>
+    <t>#f9f0ed</t>
+  </si>
+  <si>
+    <t>水性树脂改性机理及特性配伍总表（高清图谱版）</t>
+  </si>
+  <si>
+    <t>胶种</t>
+  </si>
+  <si>
+    <t>剪切强度</t>
+  </si>
+  <si>
+    <t>耐温范围</t>
+  </si>
+  <si>
+    <t>核心优势</t>
+  </si>
+  <si>
+    <t>主要缺点</t>
+  </si>
+  <si>
+    <t>推荐基材</t>
+  </si>
+  <si>
+    <t>配伍禁忌</t>
+  </si>
+  <si>
+    <t>环氧树脂胶</t>
+  </si>
+  <si>
+    <t>25–35MPa</t>
+  </si>
+  <si>
+    <t>-60~150℃</t>
+  </si>
+  <si>
+    <t>高强度、低收缩、耐化学、粘接稳定</t>
+  </si>
+  <si>
+    <t>偏脆、韧性差、固化较慢</t>
+  </si>
+  <si>
+    <t>碳钢、铝、不锈钢、玻璃钢、ABS、PC、陶瓷</t>
+  </si>
+  <si>
+    <t>禁 PE/PP/PTFE、油性基材、不可与有机硅混用</t>
+  </si>
+  <si>
+    <t>聚氨酯结构胶</t>
+  </si>
+  <si>
+    <t>15–25MPa</t>
+  </si>
+  <si>
+    <t>-40~120℃</t>
+  </si>
+  <si>
+    <t>高弹性、耐冲击、柔性好、低温优秀</t>
+  </si>
+  <si>
+    <t>耐湿热一般、怕湿气、强度中等</t>
+  </si>
+  <si>
+    <t>铝、复合材料、塑料、木材、玻璃</t>
+  </si>
+  <si>
+    <t>禁强酸强碱、长期高温、氟硅材料</t>
+  </si>
+  <si>
+    <t>丙烯酸结构胶</t>
+  </si>
+  <si>
+    <t>20–30MPa</t>
+  </si>
+  <si>
+    <t>-30~120℃</t>
+  </si>
+  <si>
+    <t>室温快固、无需底涂、多基材通用</t>
+  </si>
+  <si>
+    <t>收缩较大、有气味、耐候一般</t>
+  </si>
+  <si>
+    <t>金属、ABS、PC、PMMA、玻璃钢</t>
+  </si>
+  <si>
+    <t>禁纯 PP/PE、PTFE、高含硫基材</t>
+  </si>
+  <si>
+    <t>有机硅结构胶</t>
+  </si>
+  <si>
+    <t>1–5MPa</t>
+  </si>
+  <si>
+    <t>-60~200℃</t>
+  </si>
+  <si>
+    <t>超耐候、耐高低温、绝缘防水</t>
+  </si>
+  <si>
+    <t>强度低、不能承重、固化慢</t>
+  </si>
+  <si>
+    <t>玻璃、陶瓷、户外密封、电子</t>
+  </si>
+  <si>
+    <t>禁结构受力、不可与环氧 / PU 混用</t>
+  </si>
+  <si>
+    <t>MS 改性硅烷胶</t>
+  </si>
+  <si>
+    <t>8–15MPa</t>
+  </si>
+  <si>
+    <t>-40~90℃</t>
+  </si>
+  <si>
+    <t>环保无溶剂、耐候、易施工、内应力小</t>
+  </si>
+  <si>
+    <t>强度一般、不耐高温</t>
+  </si>
+  <si>
+    <t>玻璃、铝材、塑料、家装、装配式</t>
+  </si>
+  <si>
+    <t>禁长期高温、强化学腐蚀环境</t>
+  </si>
+  <si>
+    <t>进口耐高温树脂选型与改性图谱（表格版）</t>
+  </si>
+  <si>
+    <t>树脂类型</t>
+  </si>
+  <si>
+    <t>进口代表品牌/型号</t>
+  </si>
+  <si>
+    <t>耐温性能（长期/短期）</t>
+  </si>
+  <si>
+    <t>Tg值</t>
+  </si>
+  <si>
+    <t>主要短板</t>
+  </si>
+  <si>
+    <t>改性方向及效果</t>
+  </si>
+  <si>
+    <t>适配场景</t>
+  </si>
+  <si>
+    <t>耐高温环氧树脂</t>
+  </si>
+  <si>
+    <t>DIC HP-4710、亨斯曼MY-720、陶氏DER</t>
+  </si>
+  <si>
+    <t>120-180℃ / 200-250℃</t>
+  </si>
+  <si>
+    <t>120-200℃</t>
+  </si>
+  <si>
+    <t>粘结性强、力学性能好、电绝缘优异、工艺成熟、性价比高</t>
+  </si>
+  <si>
+    <t>高温易脆、耐候性一般、超200℃易降解</t>
+  </si>
+  <si>
+    <t>忌强极性溶剂+高温、大量酯类增塑剂</t>
+  </si>
+  <si>
+    <t>1. 有机硅改性（耐温提升至180℃）                                              2. 聚酰亚胺接枝（耐温提升190℃）                                                       3. 酚醛共混（耐温150-160℃）</t>
+  </si>
+  <si>
+    <t>120-180℃场景、结构粘接、电子灌封</t>
+  </si>
+  <si>
+    <t>有机硅树脂</t>
+  </si>
+  <si>
+    <t>迈图、瓦克、信越</t>
+  </si>
+  <si>
+    <t>250-300℃ / 350-400℃</t>
+  </si>
+  <si>
+    <t>无明确固定值（随牌号差异较大）</t>
+  </si>
+  <si>
+    <t>耐候性优、耐UV、低温柔软、热稳定性强、不黄变</t>
+  </si>
+  <si>
+    <t>力学强度偏低、附着力一般、固化温度高</t>
+  </si>
+  <si>
+    <t>忌强酸强碱、强氧化体系、大量胺类固化剂</t>
+  </si>
+  <si>
+    <t>1. 环氧改性（增粘增硬）                     2. 聚酯共混（改善力学性能）            3. 苯基改性（提升耐温性能）</t>
+  </si>
+  <si>
+    <t>200-280℃场景、耐候/户外/防腐</t>
+  </si>
+  <si>
+    <t>聚酰亚胺（PI/BMI）</t>
+  </si>
+  <si>
+    <t>杜邦、宇部兴产、沙比克</t>
+  </si>
+  <si>
+    <t>250-300℃ / 400℃+</t>
+  </si>
+  <si>
+    <t>高温强度高、尺寸稳定、耐辐射、阻燃、低介电</t>
+  </si>
+  <si>
+    <t>脆性大、工艺复杂、溶解性差、成本高</t>
+  </si>
+  <si>
+    <t>忌强极性非质子溶剂高温、水、醇类、酸性体系</t>
+  </si>
+  <si>
+    <t>1. 联苯型改性（增韧）                         2. 硅氧烷嵌段改性（降脆）                 3. 氟取代改性（低吸湿）</t>
+  </si>
+  <si>
+    <t>300℃+场景、极端高温/结构件、航空/高端电子</t>
+  </si>
+  <si>
+    <t>氰酸酯树脂</t>
+  </si>
+  <si>
+    <t>亨斯曼、朗盛</t>
+  </si>
+  <si>
+    <t>200-240℃ / 无明确短期耐温（随牌号差异）</t>
+  </si>
+  <si>
+    <t>200-260℃</t>
+  </si>
+  <si>
+    <t>高频电性能优、阻燃、耐湿热、力学性能均衡</t>
+  </si>
+  <si>
+    <t>固化条件苛刻、成本高、对湿气敏感</t>
+  </si>
+  <si>
+    <t>忌胺类促进剂过量、水、羟基化合物、强酸</t>
+  </si>
+  <si>
+    <t>1. 环氧共混（降低固化温度）             2. 橡胶增韧（提升抗冲击性）            3. 有机硅接枝（提升耐候性）</t>
+  </si>
+  <si>
+    <t>250-300℃场景、高频/航空/高端电子</t>
+  </si>
+  <si>
+    <t>苯并恶嗪树脂</t>
+  </si>
+  <si>
+    <t>日本化成、亨斯曼</t>
+  </si>
+  <si>
+    <t>热失重5%＞380℃（无明确长短期区分）</t>
+  </si>
+  <si>
+    <t>本征阻燃、低烟低毒、低吸水、完美兼容环氧体系、近零收缩</t>
+  </si>
+  <si>
+    <t>固化温度偏高、部分牌号脆性大</t>
+  </si>
+  <si>
+    <t>忌强酸性环境、高温水接触</t>
+  </si>
+  <si>
+    <t>1. 双酚F型改性（降低粘度）              2. 磷氮协同改性（阻燃升级）                3. 纳米蒙脱土改性（增强）</t>
+  </si>
+  <si>
+    <t>需阻燃/低烟/低毒场景、兼容环氧体系的高温场景</t>
+  </si>
+  <si>
+    <t>聚酰胺酰亚胺（PAI）</t>
+  </si>
+  <si>
+    <t>杜邦、宇部兴产</t>
+  </si>
+  <si>
+    <t>300℃+ / 450℃+（短期）</t>
+  </si>
+  <si>
+    <t>兼具PI的耐高温和PA的韧性、力学强度高、耐化学腐蚀</t>
+  </si>
+  <si>
+    <t>成本高、加工难度大、溶解性较差</t>
+  </si>
+  <si>
+    <t>忌强碱性体系、高温水、强极性溶剂</t>
+  </si>
+  <si>
+    <t>1. 氟改性（提升耐化学性）                 2. 碳纤维增强（提升强度）                  3. 弹性体增韧（改善加工性）</t>
+  </si>
+  <si>
+    <t>300℃+场景、极端高温结构件、耐化学腐蚀场景</t>
+  </si>
+  <si>
+    <t>陶瓷化树脂</t>
+  </si>
+  <si>
+    <t>特种进口牌号（无通用主流品牌）</t>
+  </si>
+  <si>
+    <t>500℃+ / 600℃+（短期）</t>
+  </si>
+  <si>
+    <t>无明确固定值</t>
+  </si>
+  <si>
+    <t>超高温稳定性极强、阻燃性优异、耐高温氧化</t>
+  </si>
+  <si>
+    <t>力学韧性差、加工工艺复杂、成本极高</t>
+  </si>
+  <si>
+    <t>忌强还原体系、高温下接触强酸强碱</t>
+  </si>
+  <si>
+    <t>1. 纳米陶瓷微粉填充（提升稳定性）    2. 硅氧烷改性（改善韧性）</t>
+  </si>
+  <si>
+    <t>500℃+极端高温场景、高温防腐、特种结构件</t>
+  </si>
+  <si>
+    <t>PBI（聚苯并咪唑）</t>
+  </si>
+  <si>
+    <t>杜邦、特种进口牌号</t>
+  </si>
+  <si>
+    <t>500℃+ / 700℃+（短期）</t>
+  </si>
+  <si>
+    <t>耐高温性能极强、耐辐射、耐化学腐蚀、阻燃</t>
+  </si>
+  <si>
+    <t>成本极高、加工难度极大、脆性大、溶解性极差</t>
+  </si>
+  <si>
+    <t>忌强氧化性酸、高温下接触碱金属</t>
+  </si>
+  <si>
+    <t>1. 聚酰亚胺共混（改善溶解性）          2. 碳纤维增强（提升强度）</t>
+  </si>
+  <si>
+    <t>500℃+极端高温场景、航空航天、特种高端领域</t>
+  </si>
+  <si>
+    <t>核心特性</t>
+  </si>
+  <si>
+    <t>主要优势</t>
+  </si>
+  <si>
+    <t>固化方式</t>
+  </si>
+  <si>
+    <t>适配基材</t>
+  </si>
+  <si>
+    <t>配伍 / 使用禁忌</t>
+  </si>
+  <si>
+    <t>环氧树脂胶 (EP)</t>
+  </si>
+  <si>
+    <t>高强度、高刚性、低收缩、耐化学</t>
+  </si>
+  <si>
+    <t>结构强度高、尺寸稳定、粘接广泛</t>
+  </si>
+  <si>
+    <t>-60℃~150℃</t>
+  </si>
+  <si>
+    <t>双组分 / 加热固化</t>
+  </si>
+  <si>
+    <t>金属、碳纤维、玻璃、陶瓷、ABS/PC/PVC</t>
+  </si>
+  <si>
+    <t>难粘塑料 (PP/PE/PTFE)、软质橡胶、长期强 UV 户外</t>
+  </si>
+  <si>
+    <t>聚氨酯胶 (PU)</t>
+  </si>
+  <si>
+    <t>高弹性、抗冲击、耐低温、柔韧</t>
+  </si>
+  <si>
+    <t>韧性好、适配异种材料、吸震</t>
+  </si>
+  <si>
+    <t>-40℃~120℃</t>
+  </si>
+  <si>
+    <t>湿气 / 双组分固化</t>
+  </si>
+  <si>
+    <t>金属、塑料、木材、玻璃、橡胶、泡沫</t>
+  </si>
+  <si>
+    <t>强酸强碱、长期高温、部分增塑剂 PVC</t>
+  </si>
+  <si>
+    <t>丙烯酸酯结构胶 (SGA)</t>
+  </si>
+  <si>
+    <t>快速固化、施工便捷</t>
+  </si>
+  <si>
+    <t>5~30min 快固、多数免底涂</t>
+  </si>
+  <si>
+    <t>-40℃~130℃</t>
+  </si>
+  <si>
+    <t>双组分室温固化</t>
+  </si>
+  <si>
+    <t>金属、亚克力、ABS、PC、碳纤维</t>
+  </si>
+  <si>
+    <t>纯 PP/PE/PTFE、长期户外暴晒易黄变</t>
+  </si>
+  <si>
+    <t>有机硅胶 (SR)</t>
+  </si>
+  <si>
+    <t>户外抗 UV、长期耐老化、柔性好</t>
+  </si>
+  <si>
+    <t>-60℃~200℃</t>
+  </si>
+  <si>
+    <t>湿气固化</t>
+  </si>
+  <si>
+    <t>玻璃、铝材、陶瓷、石材、一般塑料</t>
+  </si>
+  <si>
+    <t>不可承重结构、粘接后难上漆、油性基材</t>
+  </si>
+  <si>
+    <t>厌氧胶</t>
+  </si>
+  <si>
+    <t>缺氧固化、锁固密封</t>
+  </si>
+  <si>
+    <t>金属专用、防松防锈、密封一体</t>
+  </si>
+  <si>
+    <t>-55℃~150℃</t>
+  </si>
+  <si>
+    <t>隔绝空气固化</t>
+  </si>
+  <si>
+    <t>仅限金属 (钢 / 铁 / 铜 / 铝)、螺纹 / 法兰</t>
+  </si>
+  <si>
+    <t>非金属、大间隙、有氧露天、塑料橡胶</t>
   </si>
 </sst>
 </file>
@@ -74,13 +639,86 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="48">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="汉仪旗黑-55简"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="汉仪旗黑-55简"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="汉仪旗黑-55简"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="汉仪旗黑-55简"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="汉仪旗黑-55简"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="汉仪旗黑-55简"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="汉仪旗黑-55简"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="汉仪旗黑-55简"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="汉仪旗黑-55简"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="汉仪旗黑-55简"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -91,10 +729,52 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -106,6 +786,35 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF2972F4"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFCE9178"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFFBF1D7"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
@@ -113,18 +822,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF1450B8"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -264,7 +987,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="65">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -273,25 +996,193 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE7BF40"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA4DD52"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1781B5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFD8134"/>
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4167B1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF0F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD62828"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8E9A1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE58889"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9F0ED"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6B496A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6090B8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6E3C3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AE966"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF718771"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF978A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00000E"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA515F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF664B3A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6F94CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE07563"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41BBCB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4D613C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF707899"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70C588"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,12 +1373,60 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="13">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFE3E4E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFE3E4E6"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -591,172 +1530,359 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="35" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="36" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="36" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="37" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -812,6 +1938,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <mruColors>
+      <color rgb="00F4F207"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1142,13 +2273,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="1" max="1" width="27.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1159,49 +2290,82 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="6"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
+      <c r="C2" s="62"/>
+    </row>
+    <row r="3" ht="15" spans="1:7">
+      <c r="A3" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="6"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
+      <c r="C3" s="62"/>
+    </row>
+    <row r="4" ht="15" spans="1:7">
+      <c r="A4" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="62"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="66" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="62"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="68" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="62"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="69"/>
+      <c r="B7" s="69"/>
+      <c r="C7" s="69"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="69"/>
+      <c r="B8" s="69"/>
+      <c r="C8" s="69"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="F16" s="70" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="71" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="6:7">
+      <c r="F17" s="70" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="72" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A4" r:id="rId1"/>
-    <hyperlink ref="A5" r:id="rId2"/>
-    <hyperlink ref="A6" r:id="rId3"/>
-    <hyperlink ref="A2" r:id="rId4" display="read.susurrop.top" tooltip="http://susurrop.top"/>
-    <hyperlink ref="A3" r:id="rId5" display="read.panoramafind.fun" tooltip="http://panoramafind.fun"/>
+    <hyperlink ref="F16" r:id="rId1" display="spuddles.fun"/>
+    <hyperlink ref="F17" r:id="rId2" display="moilfuns.fun"/>
+    <hyperlink ref="A5" r:id="rId3" display="finonewsx.com" tooltip="http://finonewsx.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1211,40 +2375,148 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="2" outlineLevelCol="2"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="39"/>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="54" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="39"/>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:5">
+      <c r="A4" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="56" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="39"/>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4">
         <v>9</v>
       </c>
-      <c r="B3" s="3" t="s">
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="39"/>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
         <v>10</v>
       </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="58" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="39"/>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="59"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="invicts.site"/>
-    <hyperlink ref="A3" r:id="rId2" display="halcyons.cloud"/>
+    <hyperlink ref="D5" r:id="rId1" display="1"/>
+    <hyperlink ref="D6" r:id="rId1" display="2"/>
+    <hyperlink ref="E7" r:id="rId1"/>
+    <hyperlink ref="D7" r:id="rId1"/>
+    <hyperlink ref="D13" r:id="rId1"/>
+    <hyperlink ref="D14" r:id="rId1"/>
+    <hyperlink ref="D19" r:id="rId1"/>
+    <hyperlink ref="E19" r:id="rId1"/>
+    <hyperlink ref="D20" r:id="rId1"/>
+    <hyperlink ref="E20" r:id="rId1"/>
+    <hyperlink ref="D25" r:id="rId1"/>
+    <hyperlink ref="E25" r:id="rId1"/>
+    <hyperlink ref="D26" r:id="rId1"/>
+    <hyperlink ref="E26" r:id="rId1"/>
+    <hyperlink ref="D31" r:id="rId1"/>
+    <hyperlink ref="E31" r:id="rId1"/>
+    <hyperlink ref="D32" r:id="rId1"/>
+    <hyperlink ref="E32" r:id="rId1"/>
+    <hyperlink ref="D8" r:id="rId1"/>
+    <hyperlink ref="D10" r:id="rId1"/>
+    <hyperlink ref="D12" r:id="rId1"/>
+    <hyperlink ref="D16" r:id="rId1"/>
+    <hyperlink ref="D18" r:id="rId1"/>
+    <hyperlink ref="D22" r:id="rId1"/>
+    <hyperlink ref="D24" r:id="rId1"/>
+    <hyperlink ref="D28" r:id="rId1"/>
+    <hyperlink ref="D30" r:id="rId1"/>
+    <hyperlink ref="D9" r:id="rId1"/>
+    <hyperlink ref="D11" r:id="rId1"/>
+    <hyperlink ref="D15" r:id="rId1"/>
+    <hyperlink ref="D17" r:id="rId1"/>
+    <hyperlink ref="D21" r:id="rId1"/>
+    <hyperlink ref="D23" r:id="rId1"/>
+    <hyperlink ref="D27" r:id="rId1"/>
+    <hyperlink ref="D29" r:id="rId1"/>
+    <hyperlink ref="D33" r:id="rId1"/>
+    <hyperlink ref="A2" r:id="rId2" display="sylthyn.com" tooltip="http://sylthyn.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1254,9 +2526,876 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="18.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="46" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="46" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="48"/>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" s="46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="50"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+    </row>
+    <row r="5" ht="15" spans="1:6">
+      <c r="A5" s="50"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="51"/>
+    </row>
+    <row r="6" ht="15" spans="1:6">
+      <c r="A6" s="50"/>
+      <c r="B6" s="50"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="51"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="D7" s="46"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="D8" s="46"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="D9" s="46"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="D10" s="46"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="D11" s="46"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="D12" s="46"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A5" r:id="rId1" tooltip="https://skyssea.com"/>
+    <hyperlink ref="A6" r:id="rId2" tooltip="https://sunseabc.com"/>
+    <hyperlink ref="A2" r:id="rId3" display="play.seatranquil.com" tooltip="http://seatranquil.com"/>
+    <hyperlink ref="A3" r:id="rId3" display="sec.seatranquil.com" tooltip="http://seatranquil.com"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="26.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:5">
+      <c r="A2" s="37"/>
+      <c r="B2" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:5">
+      <c r="A3" s="37"/>
+      <c r="B3" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" ht="16.5" spans="1:5">
+      <c r="A4" s="42"/>
+      <c r="B4" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="45"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="45"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="45"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="45"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A6" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="15.25" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="25.875" customWidth="1"/>
+    <col min="7" max="7" width="21.125" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="12.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="31.5" spans="1:10">
+      <c r="A1" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="11"/>
+    </row>
+    <row r="3" ht="15" spans="1:10">
+      <c r="A3" s="26"/>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:10">
+      <c r="A4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" ht="83" customHeight="1" spans="1:10">
+      <c r="A5" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J5" s="28"/>
+    </row>
+    <row r="6" ht="76" customHeight="1" spans="1:10">
+      <c r="A6" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" ht="75" customHeight="1" spans="1:10">
+      <c r="A7" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" ht="75" customHeight="1" spans="1:10">
+      <c r="A8" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" ht="70" customHeight="1" spans="1:10">
+      <c r="A9" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" ht="97" customHeight="1" spans="1:10">
+      <c r="A10" s="32"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+    </row>
+    <row r="11" ht="97" customHeight="1" spans="1:10">
+      <c r="A11" s="32"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+    </row>
+    <row r="12" ht="15.75" spans="1:10">
+      <c r="A12" s="35"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="36"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="2" max="2" width="13.125" customWidth="1"/>
+    <col min="3" max="3" width="18.125" customWidth="1"/>
+    <col min="5" max="5" width="14.625" customWidth="1"/>
+    <col min="6" max="6" width="11.75" customWidth="1"/>
+    <col min="7" max="7" width="13.375" customWidth="1"/>
+    <col min="8" max="8" width="27.625" style="9" customWidth="1"/>
+    <col min="9" max="9" width="12.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="31.5" spans="1:9">
+      <c r="A1" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" ht="15" spans="1:9">
+      <c r="A2" s="11"/>
+    </row>
+    <row r="3" ht="27.75" spans="1:9">
+      <c r="A3" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" ht="62" customHeight="1" spans="1:9">
+      <c r="A4" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" ht="49" customHeight="1" spans="1:9">
+      <c r="A5" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" ht="67" customHeight="1" spans="1:9">
+      <c r="A6" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" ht="65" customHeight="1" spans="1:9">
+      <c r="A7" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" ht="64" customHeight="1" spans="1:9">
+      <c r="A8" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9" ht="64" customHeight="1" spans="1:9">
+      <c r="A9" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="10" ht="59" customHeight="1" spans="1:9">
+      <c r="A10" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" ht="54.75" spans="1:9">
+      <c r="A11" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:9">
+      <c r="A12" s="23"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="24"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
+  <cols>
+    <col min="2" max="2" width="9.875" customWidth="1"/>
+    <col min="3" max="3" width="11.125" customWidth="1"/>
+    <col min="4" max="4" width="14.125" customWidth="1"/>
+    <col min="5" max="5" width="11.25" customWidth="1"/>
+    <col min="6" max="6" width="14.5" customWidth="1"/>
+    <col min="7" max="7" width="19.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="17.25" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="2" ht="94" customHeight="1" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" ht="66.75" spans="1:10">
+      <c r="A3" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="J3" s="5"/>
+    </row>
+    <row r="4" ht="74" customHeight="1" spans="1:10">
+      <c r="A4" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5" ht="66.75" spans="1:10">
+      <c r="A5" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="6" ht="75" customHeight="1" spans="1:10">
+      <c r="A6" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
